--- a/outputs/daily/hr_rankings_2026-10-19.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-19.xlsx
@@ -815,12 +815,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -845,14 +845,26 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>56.1</v>
+        <v>53.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -866,33 +878,31 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>61.9</v>
+        <v>48.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R2" t="n">
         <v>52.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>37.8</v>
+        <v>28.9</v>
       </c>
       <c r="V2" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>48</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
           <t>No</t>
@@ -900,24 +910,24 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -930,7 +940,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
@@ -947,12 +957,12 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -962,93 +972,117 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.2549</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1082,56 +1116,16 @@
         </is>
       </c>
       <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
-        </is>
-      </c>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1139,12 +1133,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1154,7 +1148,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1169,14 +1163,26 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>54.1</v>
+        <v>53.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1194,27 +1200,29 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>48.9</v>
+        <v>61.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R3" t="n">
         <v>52.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U3" t="n">
-        <v>28.9</v>
+        <v>37.8</v>
       </c>
       <c r="V3" t="n">
-        <v>50</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>48</v>
+      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1222,24 +1230,24 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -1252,7 +1260,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr"/>
@@ -1269,12 +1277,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1284,93 +1292,117 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.1639</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+          <t>0.2549</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1404,16 +1436,56 @@
         </is>
       </c>
       <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="inlineStr"/>
-      <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1516,7 +1588,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1633,7 +1705,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>72.67</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1688,7 +1760,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1834,7 +1906,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2006,7 +2078,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2057,12 +2129,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2087,14 +2159,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>50.5</v>
+        <v>47.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2112,22 +2196,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>52.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2140,24 +2224,24 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -2170,7 +2254,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr"/>
@@ -2187,12 +2271,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2202,12 +2286,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2217,78 +2301,102 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1288</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>0.1617</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2339,12 +2447,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2369,14 +2477,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>50.3</v>
+        <v>47.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2394,22 +2514,22 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>43.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R7" t="n">
         <v>52.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2422,24 +2542,24 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -2452,7 +2572,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -2469,12 +2589,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2484,12 +2604,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -2499,78 +2619,102 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>0.1288</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2716,7 +2860,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2888,7 +3032,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3034,7 +3178,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -3206,7 +3350,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3324,7 +3468,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="Q10" t="n">
         <v>31.6</v>
@@ -3352,7 +3496,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -3464,7 +3608,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3524,7 +3668,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3642,7 +3786,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q11" t="n">
         <v>33.4</v>
@@ -3670,7 +3814,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -3782,12 +3926,12 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -3842,7 +3986,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -3923,14 +4067,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3951,16 +4107,16 @@
         <v>10.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R12" t="n">
         <v>52.6</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
         <v>70.59999999999999</v>
@@ -3976,24 +4132,24 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4006,7 +4162,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -4043,7 +4199,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4088,12 +4244,12 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -4116,15 +4272,39 @@
           <t>0.151</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4270,7 +4450,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -4442,7 +4622,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4588,7 +4768,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -4760,7 +4940,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4811,12 +4991,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4841,14 +5021,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4866,22 +5058,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R15" t="n">
         <v>52.6</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>15.3</v>
+        <v>0.8</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -4894,24 +5086,24 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4924,7 +5116,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -4941,12 +5133,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -4956,12 +5148,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -4971,78 +5163,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>0.1044</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5093,24 +5309,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -5123,14 +5339,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5144,26 +5372,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R16" t="n">
         <v>52.6</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>19.5</v>
+        <v>38.3</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5176,24 +5404,24 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -5206,7 +5434,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -5223,12 +5451,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -5238,12 +5466,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5253,78 +5481,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>0.0707</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5375,24 +5627,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -5405,17 +5657,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5424,7 +5676,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>34.8</v>
+        <v>34.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5442,22 +5694,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R17" t="n">
         <v>52.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>38.3</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5470,12 +5722,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -5517,12 +5769,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5532,12 +5784,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5547,102 +5799,102 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5693,12 +5945,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5723,12 +5975,24 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L18" t="n">
         <v>34.5</v>
       </c>
@@ -5748,22 +6012,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.6</v>
+        <v>12.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R18" t="n">
         <v>52.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T18" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -5776,24 +6040,24 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -5806,7 +6070,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr"/>
@@ -5828,22 +6092,22 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -5853,78 +6117,102 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.03</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>98.4446</t>
+          <t>99.0812</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0789</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2809</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.0731</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>0.1186</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6008,11 +6296,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>33.8</v>
+        <v>31.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6033,7 +6333,7 @@
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>31.5</v>
       </c>
       <c r="R19" t="n">
         <v>52.6</v>
@@ -6058,24 +6358,24 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -6088,7 +6388,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr"/>
@@ -6125,7 +6425,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -6170,7 +6470,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>68.35</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -6198,15 +6498,39 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -6663,12 +6987,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -6678,7 +7002,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -6693,14 +7017,26 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>56.1</v>
+        <v>53.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6714,33 +7050,31 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>61.9</v>
+        <v>48.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R2" t="n">
         <v>52.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>37.8</v>
+        <v>28.9</v>
       </c>
       <c r="V2" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>48</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
           <t>No</t>
@@ -6748,24 +7082,24 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -6778,7 +7112,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr"/>
@@ -6795,12 +7129,12 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -6810,93 +7144,117 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.2549</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -6930,56 +7288,16 @@
         </is>
       </c>
       <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
-        </is>
-      </c>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -6987,12 +7305,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -7002,7 +7320,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -7017,14 +7335,26 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>54.1</v>
+        <v>53.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7042,27 +7372,29 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>48.9</v>
+        <v>61.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R3" t="n">
         <v>52.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U3" t="n">
-        <v>28.9</v>
+        <v>37.8</v>
       </c>
       <c r="V3" t="n">
-        <v>50</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>48</v>
+      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>No</t>
@@ -7070,24 +7402,24 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -7100,7 +7432,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr"/>
@@ -7117,12 +7449,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -7132,93 +7464,117 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.1639</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+          <t>0.2549</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7252,16 +7608,56 @@
         </is>
       </c>
       <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="inlineStr"/>
-      <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>Ballpark Pal top hitter 27.9%; best park/weather on slate</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7364,7 +7760,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -7481,7 +7877,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>72.67</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -7536,7 +7932,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -7682,7 +8078,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -7854,7 +8250,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -7905,12 +8301,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7935,14 +8331,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>50.5</v>
+        <v>47.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7960,22 +8368,22 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>52.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -7988,24 +8396,24 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8018,7 +8426,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr"/>
@@ -8035,12 +8443,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -8050,12 +8458,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -8065,78 +8473,102 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1288</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>0.1617</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8187,12 +8619,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8217,14 +8649,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>50.3</v>
+        <v>47.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8242,22 +8686,22 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>43.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R7" t="n">
         <v>52.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8270,24 +8714,24 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8300,7 +8744,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -8317,12 +8761,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -8332,12 +8776,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -8347,78 +8791,102 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>0.1288</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8564,7 +9032,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -8736,7 +9204,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -8882,7 +9350,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -9054,7 +9522,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9172,7 +9640,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="Q10" t="n">
         <v>31.6</v>
@@ -9200,7 +9668,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -9312,7 +9780,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -9372,7 +9840,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9490,7 +9958,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q11" t="n">
         <v>33.4</v>
@@ -9518,7 +9986,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -9630,12 +10098,12 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -9690,7 +10158,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -9771,14 +10239,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9799,16 +10279,16 @@
         <v>10.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R12" t="n">
         <v>52.6</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
         <v>70.59999999999999</v>
@@ -9824,24 +10304,24 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -9854,7 +10334,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -9891,7 +10371,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -9936,12 +10416,12 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -9964,15 +10444,39 @@
           <t>0.151</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10118,7 +10622,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -10290,7 +10794,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10436,7 +10940,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -10608,7 +11112,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -10659,12 +11163,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -10689,14 +11193,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>36.5</v>
+        <v>35.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -10714,22 +11230,22 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R15" t="n">
         <v>52.6</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>15.3</v>
+        <v>0.8</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -10742,24 +11258,24 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -10772,7 +11288,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -10789,12 +11305,12 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -10804,12 +11320,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -10819,78 +11335,102 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>98.4476</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1223</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2522</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>0.1044</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -10941,24 +11481,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -10971,14 +11511,26 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>35.9</v>
+        <v>34.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10992,26 +11544,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>33.4</v>
       </c>
       <c r="R16" t="n">
         <v>52.6</v>
       </c>
       <c r="S16" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>19.5</v>
+        <v>38.3</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11024,24 +11576,24 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -11054,7 +11606,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -11071,12 +11623,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -11086,12 +11638,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11101,78 +11653,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>0.0707</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>6.85</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>36.39</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>87.72</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>0.1417</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>28.41</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11223,24 +11799,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -11253,17 +11829,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -11272,7 +11848,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>34.8</v>
+        <v>34.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11290,22 +11866,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>7.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R17" t="n">
         <v>52.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>38.3</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11318,12 +11894,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -11365,12 +11941,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11380,12 +11956,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -11395,102 +11971,102 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -11541,12 +12117,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>663743</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>Nick Fortes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -11571,12 +12147,24 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L18" t="n">
         <v>34.5</v>
       </c>
@@ -11596,22 +12184,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.6</v>
+        <v>12.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R18" t="n">
         <v>52.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T18" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -11624,24 +12212,24 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -11654,7 +12242,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr"/>
@@ -11676,22 +12264,22 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 2/17, 1 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -11701,78 +12289,102 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.03</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>98.4446</t>
+          <t>99.0812</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.3248</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0789</t>
+          <t>0.093</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2809</t>
+          <t>0.2721</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>72.49</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>50.84</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.0731</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>0.1186</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -11856,11 +12468,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>33.8</v>
+        <v>31.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11881,7 +12505,7 @@
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>31.5</v>
       </c>
       <c r="R19" t="n">
         <v>52.6</v>
@@ -11906,24 +12530,24 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -11936,7 +12560,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr"/>
@@ -11973,7 +12597,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -12018,7 +12642,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>68.35</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -12046,15 +12670,39 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>34 deg</t>
+          <t>43 deg</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-19.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-19.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53.6</v>
+        <v>54.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -891,7 +891,7 @@
         <v>52.6</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -905,39 +905,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1158,12 +1154,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1182,7 +1178,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>53.4</v>
+        <v>53.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1196,7 +1192,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1209,7 +1205,7 @@
         <v>52.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1225,39 +1221,35 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1402,7 +1394,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1518,7 +1510,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1542,7 +1534,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.5</v>
+        <v>53.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1556,7 +1548,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1569,7 +1561,7 @@
         <v>52.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1583,39 +1575,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1760,7 +1748,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1836,7 +1824,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1860,7 +1848,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>50.5</v>
+        <v>51.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1874,7 +1862,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1887,7 +1875,7 @@
         <v>52.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1901,39 +1889,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -2078,7 +2062,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2129,12 +2113,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2154,12 +2138,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2178,7 +2162,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.4</v>
+        <v>50.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2192,11 +2176,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
         <v>32</v>
@@ -2205,13 +2189,13 @@
         <v>52.6</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2219,39 +2203,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2271,27 +2251,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2301,67 +2281,67 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -2396,7 +2376,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2447,12 +2427,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2472,12 +2452,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2496,7 +2476,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.3</v>
+        <v>48</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2510,11 +2490,11 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
         <v>32</v>
@@ -2523,13 +2503,13 @@
         <v>52.6</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -2537,39 +2517,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2589,12 +2565,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2604,7 +2580,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -2619,67 +2595,67 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -2714,7 +2690,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2790,7 +2766,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2814,7 +2790,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>47.2</v>
+        <v>47.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2828,7 +2804,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2841,7 +2817,7 @@
         <v>52.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -2855,39 +2831,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3032,7 +3004,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3088,7 +3060,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3108,7 +3080,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3132,7 +3104,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.7</v>
+        <v>46.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3146,7 +3118,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -3159,7 +3131,7 @@
         <v>52.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -3173,39 +3145,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3350,7 +3318,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3426,7 +3394,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3450,7 +3418,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44</v>
+        <v>44.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3464,7 +3432,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3477,7 +3445,7 @@
         <v>52.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -3491,39 +3459,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3668,7 +3632,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3744,7 +3708,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3768,7 +3732,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>41.1</v>
+        <v>41.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3782,7 +3746,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3795,7 +3759,7 @@
         <v>52.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -3809,39 +3773,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3986,7 +3946,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4037,12 +3997,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4062,12 +4022,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -4086,7 +4046,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>39.5</v>
+        <v>40.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4100,11 +4060,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
         <v>32</v>
@@ -4113,13 +4073,13 @@
         <v>52.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4127,39 +4087,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4179,27 +4135,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -4209,67 +4165,67 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -4304,7 +4260,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4380,7 +4336,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4404,7 +4360,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>39.4</v>
+        <v>40</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4418,7 +4374,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -4431,7 +4387,7 @@
         <v>52.6</v>
       </c>
       <c r="S13" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -4445,39 +4401,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4622,7 +4574,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4698,7 +4650,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4722,7 +4674,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>36.6</v>
+        <v>37.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4736,7 +4688,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4749,7 +4701,7 @@
         <v>52.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4763,39 +4715,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4940,7 +4888,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4991,12 +4939,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5016,12 +4964,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -5040,7 +4988,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>35.2</v>
+        <v>37</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5054,11 +5002,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>10.6</v>
       </c>
       <c r="Q15" t="n">
         <v>32</v>
@@ -5067,13 +5015,13 @@
         <v>52.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T15" t="n">
         <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5081,39 +5029,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5133,22 +5077,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -5163,67 +5107,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -5258,7 +5202,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5309,24 +5253,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -5334,7 +5278,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5344,12 +5288,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5358,7 +5302,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>34.8</v>
+        <v>36.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5372,26 +5316,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>15.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
         <v>52.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>19.5</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5399,39 +5343,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5451,12 +5391,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -5466,12 +5406,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5481,102 +5421,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5652,12 +5592,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5676,7 +5616,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>34.5</v>
+        <v>36.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5690,7 +5630,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -5703,7 +5643,7 @@
         <v>52.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -5717,39 +5657,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5894,7 +5830,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5945,24 +5881,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -5970,22 +5906,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5994,7 +5930,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>34.5</v>
+        <v>35.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6008,26 +5944,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>7</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
         <v>52.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -6035,39 +5971,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6087,27 +6019,27 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -6117,102 +6049,102 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6288,7 +6220,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6312,7 +6244,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>31.8</v>
+        <v>32.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6326,7 +6258,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -6339,7 +6271,7 @@
         <v>52.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -6353,39 +6285,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6530,7 +6458,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7012,7 +6940,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -7036,7 +6964,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53.6</v>
+        <v>54.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7050,7 +6978,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7063,7 +6991,7 @@
         <v>52.6</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -7077,39 +7005,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7254,7 +7178,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7330,12 +7254,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7354,7 +7278,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>53.4</v>
+        <v>53.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7368,7 +7292,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7381,7 +7305,7 @@
         <v>52.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -7397,39 +7321,35 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7574,7 +7494,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7690,7 +7610,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7714,7 +7634,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>52.5</v>
+        <v>53.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7728,7 +7648,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7741,7 +7661,7 @@
         <v>52.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -7755,39 +7675,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7932,7 +7848,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -8008,7 +7924,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8032,7 +7948,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>50.5</v>
+        <v>51.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -8046,7 +7962,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -8059,7 +7975,7 @@
         <v>52.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -8073,39 +7989,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8250,7 +8162,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8301,12 +8213,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8326,12 +8238,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8350,7 +8262,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.4</v>
+        <v>50.6</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8364,11 +8276,11 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
         <v>32</v>
@@ -8377,13 +8289,13 @@
         <v>52.6</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>20.9</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8391,39 +8303,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8443,27 +8351,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -8473,67 +8381,67 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -8568,7 +8476,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8619,12 +8527,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8644,12 +8552,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8668,7 +8576,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>47.3</v>
+        <v>48</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8682,11 +8590,11 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
         <v>32</v>
@@ -8695,13 +8603,13 @@
         <v>52.6</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V7" t="n">
         <v>50</v>
@@ -8709,39 +8617,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8761,12 +8665,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -8776,7 +8680,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -8791,67 +8695,67 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -8886,7 +8790,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8962,7 +8866,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -8986,7 +8890,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>47.2</v>
+        <v>47.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -9000,7 +8904,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -9013,7 +8917,7 @@
         <v>52.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -9027,39 +8931,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9204,7 +9104,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9260,7 +9160,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9280,7 +9180,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -9304,7 +9204,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.7</v>
+        <v>46.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9318,7 +9218,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -9331,7 +9231,7 @@
         <v>52.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -9345,39 +9245,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9522,7 +9418,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9598,7 +9494,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9622,7 +9518,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44</v>
+        <v>44.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9636,7 +9532,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -9649,7 +9545,7 @@
         <v>52.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -9663,39 +9559,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9840,7 +9732,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9916,7 +9808,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9940,7 +9832,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>41.1</v>
+        <v>41.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9954,7 +9846,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -9967,7 +9859,7 @@
         <v>52.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -9981,39 +9873,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -10158,7 +10046,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10209,12 +10097,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -10234,12 +10122,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -10258,7 +10146,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>39.5</v>
+        <v>40.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10272,11 +10160,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
         <v>32</v>
@@ -10285,13 +10173,13 @@
         <v>52.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10299,39 +10187,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10351,27 +10235,27 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -10381,67 +10265,67 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -10476,7 +10360,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10552,7 +10436,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -10576,7 +10460,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>39.4</v>
+        <v>40</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10590,7 +10474,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -10603,7 +10487,7 @@
         <v>52.6</v>
       </c>
       <c r="S13" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -10617,39 +10501,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10794,7 +10674,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10870,7 +10750,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10894,7 +10774,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>36.6</v>
+        <v>37.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10908,7 +10788,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -10921,7 +10801,7 @@
         <v>52.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -10935,39 +10815,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11112,7 +10988,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11163,12 +11039,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11188,12 +11064,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -11212,7 +11088,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>35.2</v>
+        <v>37</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11226,11 +11102,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>10.6</v>
       </c>
       <c r="Q15" t="n">
         <v>32</v>
@@ -11239,13 +11115,13 @@
         <v>52.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T15" t="n">
         <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11253,39 +11129,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11305,22 +11177,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -11335,67 +11207,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -11430,7 +11302,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11481,24 +11353,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -11506,7 +11378,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11516,12 +11388,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -11530,7 +11402,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>34.8</v>
+        <v>36.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11544,26 +11416,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>15.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
         <v>52.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>19.5</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11571,39 +11443,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11623,12 +11491,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -11638,12 +11506,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11653,102 +11521,102 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11824,12 +11692,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -11848,7 +11716,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>34.5</v>
+        <v>36.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11862,7 +11730,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -11875,7 +11743,7 @@
         <v>52.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -11889,39 +11757,35 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12066,7 +11930,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12117,24 +11981,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -12142,22 +12006,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -12166,7 +12030,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>34.5</v>
+        <v>35.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12180,26 +12044,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>7</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
         <v>52.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12207,39 +12071,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12259,27 +12119,27 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -12289,102 +12149,102 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12460,7 +12320,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -12484,7 +12344,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>31.8</v>
+        <v>32.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12498,7 +12358,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -12511,7 +12371,7 @@
         <v>52.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -12525,39 +12385,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12702,7 +12558,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>43 deg</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
